--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104749_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104749_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1535</v>
+        <v>2.7982</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0747</v>
+        <v>1.3116</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0788</v>
+        <v>1.4866</v>
       </c>
       <c r="G2" t="n">
         <v>2.7367</v>
@@ -610,13 +610,13 @@
         <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.4042</v>
+        <v>-1.7595</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6729</v>
+        <v>-1.436</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7313</v>
+        <v>-0.3235</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9042</v>
+        <v>1.6718</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2028</v>
+        <v>0.6663</v>
       </c>
       <c r="F3" t="n">
-        <v>2.107</v>
+        <v>1.0055</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8761</v>
+        <v>0.8414</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7518</v>
+        <v>0.3676</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8757</v>
+        <v>0.4738</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6281</v>
+        <v>0.5688</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5371</v>
+        <v>0.5688</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.909</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2481</v>
+        <v>0.2725</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2148</v>
+        <v>-0.2012</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0333</v>
+        <v>0.4738</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3658</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5039</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1382</v>
+        <v>0.2276</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3939</v>
+        <v>0.6028</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6731</v>
+        <v>0.0975</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7207</v>
+        <v>0.5053</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5918</v>
+        <v>0.696</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4294</v>
+        <v>0.5687</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1623</v>
+        <v>0.1272</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8414</v>
+        <v>3.6401</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3676</v>
+        <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4738</v>
+        <v>3.499</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5688</v>
+        <v>4.3974</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5688</v>
+        <v>0.4579</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.9394</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2725</v>
+        <v>-0.7573</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2012</v>
+        <v>-0.3168</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4738</v>
+        <v>-0.4405</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2276</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2276</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5228</v>
+        <v>-0.5783</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1394</v>
+        <v>-0.5021</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6622</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4557</v>
+        <v>0.5732</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4268</v>
+        <v>-1.0319</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9712</v>
+        <v>1.6051</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2745</v>
+        <v>1.8761</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0228</v>
+        <v>2.7518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2517</v>
+        <v>-0.8757</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8724</v>
+        <v>1.6281</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9545</v>
+        <v>2.5371</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.909</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1469</v>
+        <v>0.2481</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9774</v>
+        <v>0.2148</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1695</v>
+        <v>0.0333</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8211</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8211</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3856</v>
+        <v>0.0629</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3953</v>
+        <v>-0.156</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7809</v>
+        <v>0.2189</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4764</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9497</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.4262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0915</v>
+        <v>-0.2133</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0949</v>
+        <v>2.0715</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1864</v>
+        <v>-2.2848</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6401</v>
+        <v>-0.2745</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1411</v>
+        <v>-0.0228</v>
       </c>
       <c r="I6" t="n">
-        <v>3.499</v>
+        <v>-0.2517</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3974</v>
+        <v>0.8724</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4579</v>
+        <v>0.9545</v>
       </c>
       <c r="L6" t="n">
-        <v>3.9394</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7573</v>
+        <v>-1.1469</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3168</v>
+        <v>-0.9774</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4405</v>
+        <v>-0.1695</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8211</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.6421</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3658</v>
+        <v>-0.2834</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9758</v>
+        <v>-0.7506</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3899</v>
+        <v>0.4672</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5447</v>
+        <v>-1.4764</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3155</v>
+        <v>1.9497</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8603</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>B. JEFFERSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4988</v>
+        <v>-1.3423</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0155</v>
+        <v>1.6594</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5167</v>
+        <v>-3.0017</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.255</v>
+        <v>-0.4316</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9392</v>
+        <v>-0.3391</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3159</v>
+        <v>-0.0924</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5276</v>
+        <v>0.7025</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7379</v>
+        <v>0.8963</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7896</v>
+        <v>-0.1939</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2725</v>
+        <v>-1.134</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2012</v>
+        <v>-1.2355</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4738</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9105</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2276</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8245</v>
+        <v>0.0406</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6502</v>
+        <v>-0.1326</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1743</v>
+        <v>0.1732</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1578</v>
+        <v>-1.6342</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1578</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5799</v>
+        <v>-1.4301</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9798</v>
+        <v>-0.8613</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6001</v>
+        <v>-0.5687</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5508999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3461</v>
+        <v>-0.1963</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2091</v>
+        <v>-0.0907</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.137</v>
+        <v>-0.1057</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. JEFFERSON</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8545</v>
+        <v>-1.6973</v>
       </c>
       <c r="E9" t="n">
-        <v>1.304</v>
+        <v>-2.3708</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1585</v>
+        <v>0.6735</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4316</v>
+        <v>-1.255</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3391</v>
+        <v>-0.9392</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0924</v>
+        <v>-0.3159</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7025</v>
+        <v>-1.5276</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8963</v>
+        <v>-0.7379</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1939</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.134</v>
+        <v>0.2725</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2355</v>
+        <v>-0.2012</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1014</v>
+        <v>0.4738</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6829</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6829</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4716</v>
+        <v>0.626</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4879</v>
+        <v>0.2949</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0163</v>
+        <v>0.3311</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6342</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7237</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1243</v>
+        <v>-1.8734</v>
       </c>
       <c r="E10" t="n">
         <v>-1.454</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6703</v>
+        <v>-0.4194</v>
       </c>
       <c r="G10" t="n">
         <v>0.3526</v>
@@ -1234,13 +1234,13 @@
         <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1615</v>
+        <v>-0.9105</v>
       </c>
       <c r="T10" t="n">
         <v>-0.7667</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3947</v>
+        <v>-0.1438</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8603</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9187</v>
+        <v>-2.6017</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.939</v>
+        <v>-4.4652</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0204</v>
+        <v>1.8635</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5323</v>
@@ -1312,13 +1312,13 @@
         <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6838</v>
+        <v>-1.3669</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.882</v>
+        <v>-1.4082</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1981</v>
+        <v>0.0413</v>
       </c>
       <c r="V11" t="n">
         <v>0.387</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7832</v>
+        <v>-5.3267</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7498</v>
+        <v>-5.1052</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0333</v>
+        <v>-0.2215</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0274</v>
@@ -1390,13 +1390,13 @@
         <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6875</v>
+        <v>-1.231</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9529</v>
+        <v>-1.3083</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2655</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7025</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.745699999999999</v>
+        <v>-8.7456</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.011099999999999</v>
+        <v>-9.010899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2654000000000002</v>
+        <v>0.265299999999999</v>
       </c>
       <c r="G13" t="n">
         <v>2.3752</v>
@@ -1444,10 +1444,10 @@
         <v>6.797199999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>8.767299999999999</v>
+        <v>8.767300000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9702</v>
+        <v>-1.970199999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-4.422</v>
@@ -1468,16 +1468,16 @@
         <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.9937</v>
+        <v>-4.9936</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.1587</v>
+        <v>-6.1588</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1651</v>
+        <v>1.165</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.9889</v>
+        <v>-4.988899999999998</v>
       </c>
       <c r="W13" t="n">
         <v>5.1466</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.388</v>
+        <v>5.2419</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9055</v>
+        <v>6.6026</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5175</v>
+        <v>-1.3607</v>
       </c>
       <c r="G14" t="n">
         <v>3.1927</v>
@@ -1546,13 +1546,13 @@
         <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7024</v>
+        <v>0.5563</v>
       </c>
       <c r="T14" t="n">
-        <v>1.881</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1786</v>
+        <v>-0.0218</v>
       </c>
       <c r="V14" t="n">
         <v>1.7205</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>E. BROOKS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6255</v>
+        <v>3.981</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1172</v>
+        <v>2.8698</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5083</v>
+        <v>1.1112</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0568</v>
+        <v>1.3543</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2879</v>
+        <v>-0.4882</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2311</v>
+        <v>1.8426</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6860000000000001</v>
+        <v>1.5813</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1724</v>
+        <v>0.1444</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5135999999999999</v>
+        <v>1.4369</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7428</v>
+        <v>-0.227</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4603</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2826</v>
+        <v>0.4057</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5039</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5039</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0206</v>
+        <v>0.7177</v>
       </c>
       <c r="T15" t="n">
-        <v>1.184</v>
+        <v>-0.1165</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8366</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1578</v>
+        <v>0.3155</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2472</v>
+        <v>1.405</v>
       </c>
       <c r="X15" t="n">
         <v>-1.0895</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. BROOKS</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9183</v>
+        <v>3.5525</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8698</v>
+        <v>2.1697</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0485</v>
+        <v>1.3828</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3543</v>
+        <v>-0.0568</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4882</v>
+        <v>-0.2879</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8426</v>
+        <v>0.2311</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5813</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1444</v>
+        <v>0.1724</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4369</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.227</v>
+        <v>-0.7428</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.4603</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4057</v>
+        <v>-0.2826</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5934</v>
+        <v>2.5039</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5934</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>0.655</v>
+        <v>0.9476</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1165</v>
+        <v>0.2364</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7715</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3155</v>
+        <v>0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>1.405</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
         <v>-1.0895</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6937</v>
+        <v>3.3941</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9054</v>
+        <v>1.2608</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7883</v>
+        <v>2.1333</v>
       </c>
       <c r="G17" t="n">
         <v>3.3884</v>
@@ -1780,13 +1780,13 @@
         <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2159</v>
+        <v>0.9163</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0468</v>
+        <v>0.3085</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2627</v>
+        <v>0.6077</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2608</v>
+        <v>2.2673</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.8723</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3361</v>
+        <v>1.3951</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3239</v>
@@ -1858,13 +1858,13 @@
         <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5846</v>
+        <v>1.5912</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1152</v>
+        <v>-0.1677</v>
       </c>
       <c r="U18" t="n">
-        <v>2.6999</v>
+        <v>1.7589</v>
       </c>
       <c r="V18" t="n">
         <v>1.0895</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1416</v>
+        <v>0.9674</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3195</v>
+        <v>2.0826</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1779</v>
+        <v>-1.1152</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0767</v>
@@ -1936,13 +1936,13 @@
         <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2183</v>
+        <v>0.0441</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0468</v>
+        <v>-0.2837</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2651</v>
+        <v>0.3278</v>
       </c>
       <c r="V19" t="n">
         <v>1.6342</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4565</v>
+        <v>0.5192</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8633999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3199</v>
+        <v>1.3826</v>
       </c>
       <c r="G20" t="n">
         <v>0.8669</v>
@@ -2014,13 +2014,13 @@
         <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1161</v>
+        <v>-0.0534</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3485</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2324</v>
+        <v>0.2951</v>
       </c>
       <c r="V20" t="n">
         <v>0.6162</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2958</v>
+        <v>-0.153</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.808</v>
+        <v>-1.5711</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5122</v>
+        <v>1.4181</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0566</v>
@@ -2092,13 +2092,13 @@
         <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2392</v>
+        <v>-0.0964</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5576</v>
+        <v>-0.3207</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3184</v>
+        <v>0.2243</v>
       </c>
       <c r="V21" t="n">
         <v>0.5447</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.97</v>
+        <v>-1.2453</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.318</v>
+        <v>-2.4364</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3479</v>
+        <v>1.1911</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8457</v>
@@ -2170,13 +2170,13 @@
         <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8757</v>
+        <v>0.6004</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0926</v>
+        <v>-0.0258</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7831</v>
+        <v>0.6262</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6351</v>
+        <v>-1.9174</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1335</v>
+        <v>-2.5412</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4983</v>
+        <v>0.6238</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1045</v>
@@ -2248,13 +2248,13 @@
         <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.511</v>
+        <v>0.2067</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9758</v>
+        <v>-0.3836</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4648</v>
+        <v>0.5903</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2472</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6678</v>
+        <v>-2.2741</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9134</v>
+        <v>-2.6765</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2455</v>
+        <v>0.4024</v>
       </c>
       <c r="G24" t="n">
         <v>0.7118</v>
@@ -2326,13 +2326,13 @@
         <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1928</v>
+        <v>0.2009</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1394</v>
+        <v>0.0975</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0534</v>
+        <v>0.1035</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.1699</v>
+        <v>-5.588</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2712</v>
+        <v>-6.0343</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1013</v>
+        <v>0.4464</v>
       </c>
       <c r="G25" t="n">
         <v>-4.4252</v>
@@ -2404,13 +2404,13 @@
         <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2196</v>
+        <v>-0.6377</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9758</v>
+        <v>-0.7389</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2438</v>
+        <v>0.1013</v>
       </c>
       <c r="V25" t="n">
         <v>0.1578</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.745800000000001</v>
+        <v>8.745599999999996</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2654000000000005</v>
+        <v>-0.2650999999999977</v>
       </c>
       <c r="F26" t="n">
         <v>9.010900000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.3753</v>
+        <v>-2.375300000000001</v>
       </c>
       <c r="H26" t="n">
         <v>-5.0266</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6516</v>
+        <v>2.651599999999999</v>
       </c>
       <c r="J26" t="n">
         <v>4.4218</v>
@@ -2482,10 +2482,10 @@
         <v>14.7959</v>
       </c>
       <c r="S26" t="n">
-        <v>4.993799999999999</v>
+        <v>4.9937</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1648</v>
+        <v>-1.1649</v>
       </c>
       <c r="U26" t="n">
         <v>6.158700000000001</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104749_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104749_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-10.1358</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104749_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.1467</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
